--- a/zuffascorecard.xlsx
+++ b/zuffascorecard.xlsx
@@ -124,52 +124,52 @@
     <t>~300–700 (est.)</t>
   </si>
   <si>
-    <t>Estimated: ~300–500</t>
-  </si>
-  <si>
-    <t>Estimated: ~400–600</t>
-  </si>
-  <si>
-    <t>Estimated: ~500–800</t>
-  </si>
-  <si>
-    <t>Estimated: ~3,000–5,000</t>
-  </si>
-  <si>
-    <t>Estimated: ~1,500–2,500</t>
+    <t>~300–500 (est.)</t>
+  </si>
+  <si>
+    <t>~400–600 (est.)</t>
+  </si>
+  <si>
+    <t>~500–800 (est.)</t>
+  </si>
+  <si>
+    <t>~3,000–5,000 (est.)</t>
+  </si>
+  <si>
+    <t>~1,500–2,500 (est.)</t>
   </si>
   <si>
     <t>2,462 primary tickets sold</t>
   </si>
   <si>
-    <t>Claimed 14,000; actual est. ~3,000–5,000</t>
+    <t>Claimed 14,000; actual ~3,000–5,000 (est.)</t>
   </si>
   <si>
     <t>18,855 (announced)</t>
   </si>
   <si>
-    <t>Estimated: ~$50K–$120K</t>
-  </si>
-  <si>
-    <t>Estimated: ~$50K–$100K</t>
-  </si>
-  <si>
-    <t>Estimated: ~$60K–$120K</t>
-  </si>
-  <si>
-    <t>Estimated: ~$75K–$150K</t>
-  </si>
-  <si>
-    <t>Estimated: ~$300K–$600K</t>
-  </si>
-  <si>
-    <t>Estimated: ~$200K–$400K</t>
+    <t>~$50K–$120K (est.)</t>
+  </si>
+  <si>
+    <t>~$50K–$100K (est.)</t>
+  </si>
+  <si>
+    <t>~$60K–$120K (est.)</t>
+  </si>
+  <si>
+    <t>~$75K–$150K (est.)</t>
+  </si>
+  <si>
+    <t>~$300K–$600K (est.)</t>
+  </si>
+  <si>
+    <t>~$200K–$400K (est.)</t>
   </si>
   <si>
     <t>$354,951 primary</t>
   </si>
   <si>
-    <t>Estimated: ~$400K–$800K</t>
+    <t>~$400K–$800K (est.)</t>
   </si>
   <si>
     <t>$8,030,075.85 (announced)</t>
@@ -178,19 +178,19 @@
     <t>Combined with UFC 324: ~5M weekend viewers</t>
   </si>
   <si>
-    <t>Estimated: ~250K–500K</t>
-  </si>
-  <si>
-    <t>Estimated: ~300K–600K</t>
-  </si>
-  <si>
-    <t>Estimated: ~400K–800K</t>
-  </si>
-  <si>
-    <t>Estimated: ~350K–700K</t>
-  </si>
-  <si>
-    <t>Estimated: ~1M–2M</t>
+    <t>~250K–500K (est.)</t>
+  </si>
+  <si>
+    <t>~300K–600K (est.)</t>
+  </si>
+  <si>
+    <t>~400K–800K (est.)</t>
+  </si>
+  <si>
+    <t>~350K–700K (est.)</t>
+  </si>
+  <si>
+    <t>~1M–2M (est.)</t>
   </si>
 </sst>
 </file>
